--- a/data/availability/projects/ora/solana-west.xlsx
+++ b/data/availability/projects/ora/solana-west.xlsx
@@ -461,12 +461,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Solana West latest availability</t>
+          <t>Updated inventory for solana-west</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,16 +561,16 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>319</v>
+        <v>224</v>
       </c>
       <c r="F2" t="n">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="G2" t="n">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="H2" t="n">
         <v>76</v>
@@ -582,12 +582,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Single Family (V2)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -608,22 +608,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>337</v>
+        <v>196</v>
       </c>
       <c r="F3" t="n">
-        <v>337</v>
+        <v>196</v>
       </c>
       <c r="G3" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Single Family (V3)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Twin House</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -664,16 +664,16 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="F4" t="n">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="G4" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H4" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -682,12 +682,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Single Family (V4)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -704,26 +704,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="F5" t="n">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="G5" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -732,12 +732,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Single Family (V6)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -754,26 +754,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>196</v>
+        <v>131</v>
       </c>
       <c r="F6" t="n">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>17.3</v>
       </c>
       <c r="H6" t="n">
-        <v>30</v>
+        <v>17.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -782,17 +782,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Single Family (V7)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>5% DP + 5% after 3 months, installments over 10 years</t>
         </is>
       </c>
     </row>
@@ -804,26 +804,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Loft</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>245</v>
+        <v>149</v>
       </c>
       <c r="F7" t="n">
-        <v>245</v>
+        <v>149</v>
       </c>
       <c r="G7" t="n">
-        <v>39</v>
+        <v>20.95</v>
       </c>
       <c r="H7" t="n">
-        <v>39</v>
+        <v>20.95</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -832,17 +832,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Single Family (V8)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>5% DP + 5% after 3 months, installments over 10 years</t>
         </is>
       </c>
     </row>
@@ -854,26 +854,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Twin House</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="F8" t="n">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="G8" t="n">
-        <v>44</v>
+        <v>23.8</v>
       </c>
       <c r="H8" t="n">
-        <v>44</v>
+        <v>23.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -882,17 +882,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Single Family (Twinhouse)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>5% DP + 5% after 3 months, installments over 10 years</t>
         </is>
       </c>
     </row>
@@ -904,26 +904,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="F9" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G9" t="n">
-        <v>21</v>
+        <v>21.25</v>
       </c>
       <c r="H9" t="n">
-        <v>21</v>
+        <v>22.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -932,17 +932,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Single Family (TH Middle)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>5% DP + 5% after 3 months, installments over 10 years</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Loft</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -964,16 +964,16 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F10" t="n">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="G10" t="n">
-        <v>24</v>
+        <v>24.65</v>
       </c>
       <c r="H10" t="n">
-        <v>24</v>
+        <v>24.65</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -982,17 +982,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Single Family (TH Corner)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>5% DP + 5% after 3 months, installments over 10 years</t>
         </is>
       </c>
     </row>
@@ -1004,40 +1004,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="F11" t="n">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>15.8</v>
+        <v>26.8</v>
       </c>
       <c r="H11" t="n">
-        <v>15.8</v>
+        <v>26.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Multiple Family (2 BR Typical)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Delivery 2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1054,393 +1054,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>131</v>
+        <v>232</v>
       </c>
       <c r="F12" t="n">
-        <v>131</v>
+        <v>232</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Multiple Family (2 BR Ground)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Delivery 2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
-        <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>solana-west</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Loft</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>149</v>
-      </c>
-      <c r="F13" t="n">
-        <v>149</v>
-      </c>
-      <c r="G13" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="H13" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Finished with ACs</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Multiple Family (2 BR Loft)</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Delivery 2027</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>solana-west</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Duplex</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>174</v>
-      </c>
-      <c r="F14" t="n">
-        <v>174</v>
-      </c>
-      <c r="G14" t="n">
-        <v>23</v>
-      </c>
-      <c r="H14" t="n">
-        <v>23</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Finished with ACs</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Multiple Family (2 BR Duplex)</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Delivery 2027</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>solana-west</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>172</v>
-      </c>
-      <c r="F15" t="n">
-        <v>172</v>
-      </c>
-      <c r="G15" t="n">
-        <v>20</v>
-      </c>
-      <c r="H15" t="n">
-        <v>20</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Finished with ACs</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Multiple Family (3 BR Typical)</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Delivery 2027</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>solana-west</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>164</v>
-      </c>
-      <c r="F16" t="n">
-        <v>164</v>
-      </c>
-      <c r="G16" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Finished with ACs</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Multiple Family (3 BR Ground)</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Delivery 2027</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>solana-west</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Loft</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>193</v>
-      </c>
-      <c r="F17" t="n">
-        <v>193</v>
-      </c>
-      <c r="G17" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Finished with ACs</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Multiple Family (3 BR Loft)</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Delivery 2027</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>solana-west</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Penthouse</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>200</v>
-      </c>
-      <c r="F18" t="n">
-        <v>200</v>
-      </c>
-      <c r="G18" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Finished with ACs</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Multiple Family (3 BR Penthouse)</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Delivery 2027</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>5% DP + 5% after 3 months, installments over 10 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>solana-west</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Penthouse</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>232</v>
-      </c>
-      <c r="F19" t="n">
-        <v>232</v>
-      </c>
-      <c r="G19" t="n">
-        <v>28</v>
-      </c>
-      <c r="H19" t="n">
-        <v>28</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Finished with ACs</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Multiple Family (4 BR Penthouse)</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Delivery 2027</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
         <is>
           <t>5% DP + 5% after 3 months, installments over 10 years</t>
         </is>
@@ -1540,12 +1190,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SW-V2-01</t>
+          <t>SW-SF-V2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Single Family (V2)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1561,12 +1211,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Land 803 sqm</t>
+          <t>Land 803 SQM</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1574,7 +1224,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1601,12 +1251,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SW-V3-01</t>
+          <t>SW-SF-V3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Single Family (V3)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1622,12 +1272,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Land 506 sqm</t>
+          <t>Land 506 SQM</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1635,7 +1285,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1662,12 +1312,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SW-V4-01</t>
+          <t>SW-SF-V4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Single Family (V4)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1683,12 +1333,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Land 435 sqm</t>
+          <t>Land 435 SQM</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1696,7 +1346,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1723,12 +1373,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SW-V6-01</t>
+          <t>SW-SF-V6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Single Family (V6)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1744,12 +1394,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Land 405 sqm</t>
+          <t>Land 405 SQM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1757,7 +1407,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1784,12 +1434,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SW-V7-01</t>
+          <t>SW-SF-V7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Single Family (V7)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1805,12 +1455,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Land 305 sqm</t>
+          <t>Land 305 SQM</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1818,7 +1468,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1845,12 +1495,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SW-V8-01</t>
+          <t>SW-SF-V8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Single Family (V8)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1866,12 +1516,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Land 477 sqm</t>
+          <t>Land 477 SQM</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1879,7 +1529,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1906,16 +1556,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SW-TW-01</t>
+          <t>SW-SF-TW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Single Family (Twinhouse)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1927,12 +1577,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Land 334 sqm</t>
+          <t>Land 334 SQM</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1940,7 +1590,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1962,17 +1612,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SW-THM-01</t>
+          <t>SW-SF-THM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Single Family (TH Middle)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1988,12 +1638,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Land 205 sqm</t>
+          <t>TH Middle + Land 205 SQM</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -2001,7 +1651,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2023,17 +1673,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SW-THC-01</t>
+          <t>SW-SF-THC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Single Family (TH Corner)</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2049,12 +1699,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Land 309 sqm</t>
+          <t>TH Corner + Land 309 SQM</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -2062,7 +1712,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ready / Off-Plan</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2089,12 +1739,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SW-2BR-TYP</t>
+          <t>SW-MF-2BR-TYP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Multiple Family (2 BR Typical)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2102,7 +1752,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2110,20 +1760,20 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>126-147 sqm</t>
+          <t>126-147 SQM Typical</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15800000</v>
+        <v>17500000</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Delivery 2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2150,12 +1800,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SW-2BR-GND</t>
+          <t>SW-MF-2BR-G</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Multiple Family (2 BR Ground)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2163,7 +1813,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2171,20 +1821,20 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>131 sqm + Garden 60 sqm</t>
+          <t>131 + Garden 60 SQM</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17000000</v>
+        <v>17300000</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Delivery 2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2211,12 +1861,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SW-2BR-LOFT</t>
+          <t>SW-MF-2BR-LOFT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Multiple Family (2 BR Loft)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2224,7 +1874,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,20 +1882,20 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>149 sqm</t>
+          <t>149 SQM Loft</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>20700000</v>
+        <v>20950000</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Delivery 2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2272,12 +1922,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SW-2BR-DUP</t>
+          <t>SW-MF-2BR-DUP</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Multiple Family (2 BR Duplex)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2285,7 +1935,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2293,20 +1943,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>174 sqm</t>
+          <t>174 SQM Duplex</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>23000000</v>
+        <v>23800000</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Delivery 2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2333,12 +1983,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SW-3BR-TYP</t>
+          <t>SW-MF-3BR-TYP</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Multiple Family (3 BR Typical)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2346,7 +1996,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2354,20 +2004,20 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>163-181 sqm</t>
+          <t>163-181 SQM Typical</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>20000000</v>
+        <v>21250000</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Delivery 2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2394,12 +2044,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SW-3BR-GND</t>
+          <t>SW-MF-3BR-G</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Multiple Family (3 BR Ground)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2407,7 +2057,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2415,20 +2065,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>164 sqm + Garden 90 sqm</t>
+          <t>164 + Garden 90 SQM</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>21800000</v>
+        <v>22200000</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Delivery 2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2455,12 +2105,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SW-3BR-LOFT</t>
+          <t>SW-MF-3BR-LOFT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Multiple Family (3 BR Loft)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2468,7 +2118,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2476,20 +2126,20 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>193 sqm</t>
+          <t>193 SQM Loft</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>22500000</v>
+        <v>24650000</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Delivery 2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2516,12 +2166,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SW-3BR-PENT</t>
+          <t>SW-MF-3BR-PH</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Multiple Family (3 BR Penthouse)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2529,7 +2179,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2537,20 +2187,20 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>200 sqm + Roof 55 sqm</t>
+          <t>200 + Roof 55 SQM</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>26300000</v>
+        <v>26800000</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Delivery 2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2577,12 +2227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SW-4BR-PENT</t>
+          <t>SW-MF-4BR-PH</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Multiple Family (4 BR Penthouse)</t>
+          <t>Multiple Family</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2590,7 +2240,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2598,12 +2248,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>232 sqm + Roof 60 sqm</t>
+          <t>232 + Roof 60 SQM</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2611,7 +2261,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Delivery 2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
